--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-body-structure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Précision topographique (par exemple : supérieur, inférieur, distal, proximal).</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-modificateur-topographique-cisis</t>
@@ -1107,13 +1110,13 @@
         <v>73</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1148,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1174,13 +1177,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1231,7 +1234,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
